--- a/data/describe/CBs_and_CB_Pairs.xlsx
+++ b/data/describe/CBs_and_CB_Pairs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,384 +472,434 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A centre-back (a.k.a. CB) is a central defender in football - it's a defensive football player that is usually located in the middle of the defensive line, directly in front of their own goalkeeper. Their primary role and core responsabilities are to stop the opposition from creating chances and preventing them from scoring goals (especially through the center of the pitch), blocking shots, marking opponents, and building play from the back (with passes or ball carries). They often engage in ground duels with opposing attackers, trying to win possession or at least stop progression. They also contribute to aerial duels, interceptions, and organizing the defensive line from a tactical standpoint; thus, positional intelligence and composure are also important.</t>
+          <t>A centre-back (a.k.a. CB) is a central defender in football - it's a defensive player who is usually positioned in the middle of the defensive line, directly in front of their own goalkeeper (a.k.a. GK). Their primary role and core responsibilities are to stop the opposition from creating chances and preventing them from scoring goals (especially through the central areas of the pitch), blocking shots, marking opponents, protecting space, and organizing the defensive line from a tactical standpoint. They often engage in ground duels with opposing attackers, trying to win possession or at least stop progression, while also contributing in aerial duels, interceptions, and other defensive actions that require positional intelligence, concentration, timing, and composure.
+Nowadays, however, a CB is not only judged by its pure physical defending or anticipation. Ball-passing skills are also a major part of the role now, because CBs are often expected to help build play from the back (either through passes or ball carries), circulate possession cleanly, break the first few opposition pressure lines with accurate passes, switch play with long balls, and remain calm under pressure. A strong CB therefore adds value not only by defending well, but also by helping their team progress the ball in a controlled and tactically useful way.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>What would make a top CB?, or what would the best CB player look like?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Top CBs (or the prototype for the best CB), ideally try to be as complete and balanced as possible across the 3 main quality areas:
+- ground duels, 
+- aerial duels, and 
+- ball passing.
+Excelling in only 1 or 2 of these can still make a CB player useful, but being well-rounded across all 3 usually makes a CB more reliable, harder to exploit, more tactically flexible, and better suited to the demands of elite-level football.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>What would make a terrible CB?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A terrible CB would be one who lacks proficiency in any of the 3 main quality areas:
+- ground duels, 
+- aerial duels, and 
+- ball passing.
+Such a CB player might struggle to defend effectively, fail to contribute to building play from the back, and be easily exploited by opponents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>What would make an average CB?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>An average CB would be one who demonstrates moderate proficiency in the 3 main quality areas:
+- ground duels, 
+- aerial duels, and 
+- ball passing.
+Such a CB player might be able to perform adequately in most situations, but may not stand out as particularly strong or reliable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>What type of analyses or assessments can you perform?</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>I'm able to analyze or assess: 
-- Individual CBs themselves, 
+- Individual CB players, 
 - Comparisons between different CBs, 
 - CB-pairs themselves (where I evaluate the combined performance of 2 CBs, if they potentially were to play together), 
 - Comparisons between different CB-pairs, and 
-- Directional anchor-to-partner companion-fits (where I evaluate how well 1 CB would complement another specific CB, if they potentially were to play together).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>What qualities do we use to evaluate a CB?</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>We evaluate CBs by their ground and aerial duel qualities, and ball-passing skills. All these statistics are adjusted for the ball possession of the team the player plays for and given per 90 minutes played.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Could you answer some questions about ground duels for me?</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Of course — send them over, and I'll tackle them one after another! I'll do my best to win the second balls too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Which metrics are used to evaluate ground duels for CBs?</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Currently, I have the capability to assess the following ground duels' metrics for CB: 
-- Ground duels per-90, 
-- Interceptions per-90, 
-- Duel success rate, 
-- Possession win rate, 
-- Discipline, 
-- Card discipline.</t>
+- (Directional) Anchor-to-partner CB companion-fits (where I evaluate how well 1 CB would complement another specific CB, if they potentially were to play together).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>May I ask you another question?</t>
+          <t>What qualities do we use to evaluate a CB?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Naturally — I challenge you to a (ground) duel of Q&amp;As. Feel free to ask as many questions as you may need — let's keep the ball rolling!</t>
+          <t>We evaluate CBs by their ground and aerial duel qualities, and ball-passing skills. All these statistics are adjusted for the ball possession of the team the player plays for and given per 90 minutes played.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Could you answer some questions about ground duels for me?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Of course — send them over, and I'll tackle them one after another! I'll do my best to win the second balls too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Which metrics are used to evaluate ground duels for CBs?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Currently, I have the capability to assess the following ground duels' metrics for CB: 
+- Possession win rate, 
+- Duel success rate, 
+- Interceptions per-90, 
+- Discipline, 
+- Card discipline, and 
+- Ground duels per-90.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>May I ask you another question?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Naturally — I challenge you to a (ground) duel of Q&amp;As.
+Feel free to ask as many questions as you may need — let's keep the ball rolling!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>What does ground duels per-90 measure?</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Ground duels per-90 measures how many ground duels a CB is involved in on average every 90 minutes of play. This helps to understand how active a player is in ground duels relative to their playing time. 
 A higher ground duels per-90 indicates that the CB is more frequently engaging in defensive ground challenges, which can be a sign of their involvement and influence in defensive actions during matches. However, it's important to consider this metric in conjunction with success rates and other quality metrics, as a high volume of duels doesn't necessarily mean effective defending if the success rate is low.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>What does it imply if a CB (or CB-pair) is good or excellent in terms of ground duels per-90?</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>A CB (or CB-pair) who is good or excellent in terms of ground duels per-90 is frequently engaging in defensive ground challenges, indicating their active involvement and influence in defensive actions during matches. This suggests the CB is highly effective in their defensive duties, consistently intends to participate in ground duels and contribute to their team's defensive solidity.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>What does it imply if a CB (or CB-pair) is below average or poor in terms of ground duels per-90?</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>A CB (or CB-pair) who is below average or poor in terms of ground duels per-90 is not frequently engaging in defensive ground challenges, indicating a lack of active involvement in defensive actions during matches. This suggests the CB may struggle with their defensive duties, potentially leading to gaps in their team's defensive solidity.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>What does interceptions per-90 measure?</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Interceptions per-90 combines the number of won possessions + stopped progressions achieved by a CB (to give an idea of how many times a player successfully interrupts the opponent's play) every 90 minutes. This is particularly relevant for defenders, as it reflects their ability to break up attacks, regain possession for their team, and creating opportunities for their team to transition from defense to attack. 
 A higher interceptions per-90 indicates a CB's effectiveness in reading the game, anticipation, and making crucial and tactically intelligent defensive interventions.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>What does it imply if a CB (or CB-pair) is outstanding in terms of interceptions per-90?</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A CB (or CB-pair) who is outstanding in terms of interceptions per-90 is highly effective in reading the game, anticipating the opponent's moves, and making crucial defensive interventions. This indicates the CB is exceptional at breaking up attacks, regaining possession for their team, and creating transition opportunities from defense to attack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>What does stops per-90 or stopped progressions per-90 measure?</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Stopped progressions per-90 is a metric that focuses specifically on how many times a CB successfully stops the opponent's progress every 90 minutes. This is a key defensive action that indicates a CB's ability to disrupt the flow of the opponent's attack, even if they don't necessarily win possession straight after the (ground) duel they were involved in, but it was enough to at the very least halt the attack. 
-A higher stopped progressions per-90 value indicates a CB's effectiveness in disrupting the opponent's attacking rhythm and preventing them from advancing towards goal-scoring opportunities, which is a critical aspect of defensive performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>What does duel success rate measure?</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>(Ground) duel success rate measures the proportion of ground duels that a CB wins relative to the total number of ground duels they participated in — i.e. it reflects the percentage of duels in which the CB either won possession or successfully stopped the opponent's progress, providing a comprehensive insight into their effectiveness in defensive challenges during ground duels. 
-A higher (ground) duel success rate indicates that a CB is more effective in their (ground) duels, successfully winning possession or stopping the opponent's progress more often. This is a key indicator of a CB's ability to disrupt the opposition's play and contribute to their team's defensive solidity.</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>What does it imply if a CB (or CB-pair) is average in terms of duel success rate?</t>
+          <t>What does it imply if a CB (or CB-pair) is outstanding in terms of interceptions per-90?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A CB (or CB-pair) who is average in terms of duel success rate is performing at a moderate level in their ground duels, neither excelling nor struggling significantly. This suggests the CB is contributing to their team's defensive efforts but may have room for improvement in terms of winning possession or stopping the opponent's progress more consistently.</t>
+          <t>A CB (or CB-pair) who is outstanding in terms of interceptions per-90 is highly effective in reading the game, anticipating the opponent's moves, and making crucial defensive interventions. This indicates the CB is exceptional at breaking up attacks, regaining possession for their team, and creating transition opportunities from defense to attack.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>What does possession win rate measure?</t>
+          <t>What does stops per-90 or stopped progressions per-90 measure?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Possession win rate evaluates the percentage of ground duels in which a CB won possession for their team. It focuses specifically on the CB's ability to directly regain the ball during ground duels, which is a critical aspect of defensive performance. 
-A higher possession win rate indicates that a CB is more effective at winning the ball back for their team during ground duels, which can lead to more opportunities for their team to transition from defense to attack and can be a sign of strong defensive capabilities.</t>
+          <t>Stopped progressions per-90 is a metric that focuses specifically on how many times a CB successfully stops the opponent's progress every 90 minutes. This is a key defensive action that indicates a CB's ability to disrupt the flow of the opponent's attack, even if they don't necessarily win possession straight after the (ground or aerial) duel they were involved in, but it was enough to at the very least halt the attack. 
+A higher stopped progressions per-90 value indicates a CB's effectiveness in disrupting the opponent's attacking rhythm and preventing them from advancing towards goal-scoring opportunities, which is a critical aspect of defensive performance.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>What does it imply if a CB (or CB-pair) is good in terms of possession win rate?</t>
+          <t>What does duel success rate measure?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A CB (or CB-pair) who is good in terms of possession win rate is performing well in directly regaining the ball for their team during ground duels. This indicates strong defensive capabilities and the ability to create transition opportunities from defense to attack.</t>
+          <t>Duel success rate measures the proportion of ground (or aerial) duels that a CB wins relative to the total number of duels they participated in — i.e. it reflects the percentage of duels in which the CB either won possession or successfully stopped the opponent's progress, providing a comprehensive insight into their effectiveness in defensive challenges during ground or aerial duels. 
+A higher (ground or aerial) duel success rate indicates that a CB is more effective in their (ground or aerial) duels, successfully winning possession or stopping the opponent's progress more often. This is a key indicator of a CB's ability to disrupt the opposition's play and contribute to their team's defensive solidity.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>How is discipline defined, or what does it measure?</t>
+          <t>What does it imply if a CB (or CB-pair) is average in terms of duel success rate?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Discipline is calculated as `1 - Foul Rate`, giving a measure of how disciplined a CB is their (ground) duels. 
-A higher value indicates better discipline, as it means the player commits fewer fouls relative to the total duels they participated in — i.e. cleaner defending. This is important because committing fouls can lead to dangerous free-kicks (or even penalties) for the opposition; a lack of discipline can also result in yellow or red cards, which can be harmful to their own team. Therefore, a higher discipline score is generally seen as a positive attribute for a CB.</t>
+          <t>A CB (or CB-pair) who is average in terms of duel success rate is performing at a moderate level in their ground or aerial duels, neither excelling nor struggling significantly. This suggests the CB is contributing to their team's defensive efforts but may have room for improvement in terms of winning possession or stopping the opponent's progress more consistently.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>What does it imply if a CB (or CB-pair) is very poor in terms of discipline?</t>
+          <t>What does possession win rate measure?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A CB (or CB-pair) who is very poor in terms of discipline is committing many fouls during their (ground) duels, which can lead to dangerous free-kicks (or even penalties) for the opposition or disciplinary actions against the CB themselves. This indicates a lack of control and potentially risky behavior on the pitch.</t>
+          <t>Possession win rate evaluates the percentage of ground or aerial duels in which a CB won possession for their team. It focuses specifically on the CB's ability to directly regain the ball during duels, which is a critical aspect of defensive performance. 
+A higher possession win rate indicates that a CB is more effective at winning the ball back for their team during ground or aerial duels, which can lead to more opportunities for their team to transition from defense to attack and can be a sign of strong defensive capabilities.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>What is foul rate?</t>
+          <t>What does it imply if a CB (or CB-pair) is good in terms of possession win rate?</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Foul rates represent the share of (ground) duels in which a CB commits a foul. It provides insight into a CB's tendency to engage in physical challenges that may result in a disciplinary action (i.e. receiving a yellow or red card). 
-A higher foul rate indicates that a CB is more likely to commit fouls during their (ground) duels, which can be a concern for their team as it may lead to dangerous free-kicks (or even penalties) for the opposition or disciplinary actions against the CB themselves. Therefore, a lower foul rate is generally considered as a positive attribute for a CB.</t>
+          <t>A CB (or CB-pair) who is good in terms of possession win rate is performing well in directly regaining the ball for their team during ground or aerial duels. This indicates strong defensive capabilities and the ability to create transition opportunities from defense to attack.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>What is meant then by card discipline?</t>
+          <t>How is discipline defined, or what does it measure?</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>This metric combines the number of fouls committed with the severity of those fouls (the number of times the CB got booked — yellow and/or red cards received) to give a more nuanced view of a player's discipline in (ground) duels. A CB who commits many fouls but rarely receives bookings might be less of a disciplinary risk than a CB who commits fewer fouls but frequently receives yellow or red cards. By weighting red cards heavier than yellow cards, we can capture this difference in severity and provide a more comprehensive measure of discipline in duels. 
-Thus, a higher card discipline value indicate a CB who contests (ground) duels without accumulating (potentially dangerous) bookings. This is a positive trait, as it means the CB is able to effectively challenge opponents while minimizing the risk of disciplinary actions that could harm their own team.</t>
+          <t>Discipline is calculated as `1 - Foul Rate`, giving a measure of how disciplined a CB is in their (ground or aerial) duels. 
+A higher value indicates better discipline, as it means the player commits fewer fouls relative to the total duels they participated in — i.e. cleaner defending. This is important because committing fouls can lead to dangerous free-kicks (or even penalties) for the opposition; a lack of discipline can also result in yellow or red cards, which can be harmful to their own team. Therefore, a higher discipline score is generally seen as a positive attribute for a CB.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>What does it imply if a CB (or CB-pair) is excellent in terms of card discipline?</t>
+          <t>What does it imply if a CB (or CB-pair) is very poor in terms of discipline?</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A CB (or CB-pair) who is excellent in terms of card discipline is able to contest (ground) duels effectively while minimizing the risk of disciplinary actions. This indicates strong self-control and a low likelihood of committing fouls or receiving bookings, which is a positive attribute for their team.</t>
+          <t>A CB (or CB-pair) who is very poor in terms of discipline is committing many fouls during their (ground or aerial) duels, which can lead to dangerous free-kicks (or even penalties) for the opposition or disciplinary actions against the CB themselves. This indicates a lack of control and potentially risky behavior on the pitch.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Why are red cards weighted heavier than yellow cards?</t>
+          <t>What is foul rate?</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A higher red-card penalty is applied because a dismissal has much larger match impact than a yellow card.</t>
+          <t>Foul rates represent the share of (ground or aerial) duels in which a CB commits a foul. It provides insight into a CB's tendency to engage in physical challenges that may result in a disciplinary action (i.e. receiving a yellow or red card). 
+A higher foul rate indicates that a CB is more likely to commit fouls during their (ground or aerial) duels, which can be a concern for their team as it may lead to dangerous free-kicks (or even penalties) for the opposition or disciplinary actions against the CB themselves. Therefore, a lower foul rate is generally considered as a positive attribute for a CB.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Out of these, which are the volume metrics?</t>
+          <t>What is meant then by card discipline?</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The volume metrics are: ground duels per-90, interceptions per-90, stops (or stopped progressions) per-90.</t>
+          <t>This metric combines the number of fouls committed with the severity of those fouls (the number of times the CB got booked — yellow and/or red cards received) to give a more nuanced view of a player's discipline in (ground or aerial) duels. A CB who commits many fouls but rarely receives bookings might be less of a disciplinary risk than a CB who commits fewer fouls but frequently receives yellow or red cards. By weighting red cards heavier than yellow cards, we can capture this difference in severity and provide a more comprehensive measure of discipline in duels. 
+Thus, a higher card discipline value indicate a CB who contests (ground or aerial) duels without accumulating (potentially dangerous) bookings. This is a positive trait, as it means the CB is able to effectively challenge opponents while minimizing the risk of disciplinary actions that could harm their own team.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Why combine rate metrics with volume metrics?</t>
+          <t>What does it imply if a CB (or CB-pair) is excellent in terms of card discipline?</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rate metrics capture (ground) duel efficiency while volume metrics capture involvement, so both are needed for a balanced profile.</t>
+          <t>A CB (or CB-pair) who is excellent in terms of card discipline is able to contest (ground or aerial) duels effectively while minimizing the risk of disciplinary actions. This indicates strong self-control and a low likelihood of committing fouls or receiving bookings, which is a positive attribute for their team.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>What are z-scores?</t>
+          <t>Why are red cards weighted heavier than yellow cards?</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Z-scores are standardized scores that indicate how many standard deviations an element is from the mean. In this context, they are used to compare a CB's performance relative to their cohort.</t>
+          <t>A higher red-card penalty is applied because a dismissal has much larger match impact than a yellow card.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Please explain z-scores in simple terms.</t>
+          <t>Out of these, which are the volume metrics?</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Z-scores are a way to compare how far a CB's performance is from the average performance of their peers, measured in terms of standard deviations.</t>
+          <t>The volume metrics are: ground duels per-90, interceptions per-90, stops (or stopped progressions) per-90.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>What are standard deviations?</t>
+          <t>Why combine rate metrics with volume metrics?</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Standard deviations measure the amount of variation or dispersion in a set of values. In the context of z-scores, they indicate how spread out the performance metrics are from the mean.</t>
+          <t>Rate metrics capture (ground or aerial duels, or ball-passing) efficiency while volume metrics capture involvement, so both are needed for a balanced profile.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Please explain standard deviations in simple terms.</t>
+          <t>What are z-scores?</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Standard deviations are a measure of how much the values in a dataset vary from the mean. A small standard deviation means that the values are close to the mean, while a large standard deviation means that the values are more spread out.</t>
+          <t>Z-scores are standardized scores that indicate how many standard deviations an element is from the mean. In this context, they are used to compare a CB's performance relative to their cohort.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Please explain standard deviations as if explaining to a child.</t>
+          <t>Please explain z-scores in simple terms.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Standard deviations are a way to measure how much the numbers in a group differ from the average number. If the standard deviation is small, it means most of the numbers are close to the average. If it's big, it means the numbers are more spread out and different from each other.</t>
+          <t>Z-scores are a way to compare how far a CB's performance is from the average performance of their peers, measured in terms of standard deviations.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>How are z-scores interpreted in these metrics?</t>
+          <t>What are standard deviations?</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Z-scores are used to describe relative standing of the CB or CB-pair in question against the same cohort, not absolute universal quality. A higher z-score means better performance relative to peers, while a lower z-score indicates worse performance relative to peers.</t>
+          <t>Standard deviations measure the amount of variation or dispersion in a set of values. In the context of z-scores, they indicate how spread out the performance metrics are from the mean.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Please explain standard deviations in simple terms.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Standard deviations are a measure of how much the values in a dataset vary from the mean. A small standard deviation means that the values are close to the mean, while a large standard deviation means that the values are more spread out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Please explain standard deviations as if explaining to a child.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Standard deviations are a way to measure how much the numbers in a group differ from the average number. If the standard deviation is small, it means most of the numbers are close to the average. If it's big, it means the numbers are more spread out and different from each other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>How are z-scores interpreted in these metrics?</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Z-scores are used to describe relative standing of the CB or CB-pair in question against the same cohort, not absolute universal quality. A higher z-score means better performance relative to peers, while a lower z-score indicates worse performance relative to peers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>What interpretations are being used for different z-score ranges or values?</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>CBs or CB-Pairs holding metrics with z-score values: 
 - `≥ 1.5` = Outstanding, 
@@ -861,737 +911,1104 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>What does outstanding mean in this mapping?</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Outstanding means the metric is in the highest quality band and significantly above cohort average.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>What does poor mean in this mapping?</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Poor means the metric is in the lowest quality band and materially below cohort average.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>How should average be interpreted?</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Average means the CBs' (or CB-pair's) performance is around cohort baseline and not a clear differentiator in that particular metric.</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>How would you describe a CB or CB-pair who is not above average in any metrics?</t>
+          <t>What does outstanding mean in this mapping?</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A CB or CB-pair who is not above average in any metrics could be described as not being a standout in any area.</t>
+          <t>Outstanding means the metric is in the highest quality band and significantly above cohort average.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>How would you describe a CB or CB-pair who is above average in nearly all metrics but not excellent in any of them?</t>
+          <t>What does poor mean in this mapping?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A CB or CB-pair who is above average in nearly all metrics but not excellent in any of them is a good all-rounder.</t>
+          <t>Poor means the metric is in the lowest quality band and materially below cohort average.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>How would you describe a CB or CB-pair who is below average in nearly all metrics but not poor in any of them?</t>
+          <t>How should average be interpreted?</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A CB or CB-pair who is below average in nearly all metrics but not poor in any of them is a deficient performer, with space for improvement.</t>
+          <t>Average means the CBs' (or CB-pair's) performance is around cohort baseline and not a clear differentiator in that particular metric.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>How are yellow cards and/or red cards treated?</t>
+          <t>How would you describe a CB or CB-pair who is not above average in any metrics?</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>According to domain knowledge, higher raw card (or booking) counts represent a negative defensive control signal and should never be framed as a strength.</t>
+          <t>A CB or CB-pair who is not above average in any metrics could be described as not being a standout in any area.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>How should high a card discipline value, with low raw cards (bookings), be described?</t>
+          <t>How would you describe a CB or CB-pair who is above average in nearly all metrics but not excellent in any of them?</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>High card discipline should be described as clean duel management with low booking and dismissal exposure.</t>
+          <t>A CB or CB-pair who is above average in nearly all metrics but not excellent in any of them is a good all-rounder.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>What are the most important attributes or features for a CB (or CB-pair)?</t>
+          <t>How would you describe a CB or CB-pair who is below average in nearly all metrics but not poor in any of them?</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The most important attribute for a CB (or CB-pair) is undeniably defensive capability, as their main job is to prevent the opposing team from scoring. Some good CBs (or CB-pairs) are good at only (ground) duel success rate, but in the modern game, it is almost necessary for a CB (-pair) to be good in other aspects in order to succeed. Some teams rely on CBs (-pairs) to contribute by winning possession after (ground or aerial) duels, perform clean defending while maintaining good card discipline, and intercept passes; other teams, on the other hand, desire someone who can read the game and tactically organize the defense, has the vision and anticipation to constantly keep the opposing's strikers off-side, communicate effectively with leadership, and have the skill to build up play through quality ball-passing.</t>
+          <t>A CB or CB-pair who is below average in nearly all metrics but not poor in any of them is a deficient performer, with space for improvement.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>What are the most important metrics/data-points for a CB (or CB-pair)?</t>
+          <t>How are yellow cards and/or red cards treated?</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The ranking order of the most important metrics may be personalized by setting and tuning yourself the importance weights of the relevant metrics (for the ground duels quality at hand) using the UI sliders in this page. But generally speaking, possession win rate tends to be assigned as the most important one, as directly regaining the ball is the most valuable (ground) duel outcome. **Note:** they all **must** sum to `1.0`.</t>
+          <t>According to domain knowledge, higher raw card (or booking) counts represent a negative defensive control signal and should never be framed as a strength. But one must understand that even though this may be the general understanding, one must take into account the context of the play - for instance, committing a foul and receiving a booking as a result, in a situation where the CB stopped a dangerous counter-attack with a potential high threat value, may be evaluated as a highly valuable defensive action.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be a front-foot defender?</t>
+          <t>How should high a card discipline value, with low raw cards (bookings), be described?</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>When describing a CB to be front-foot defender, it refers to a CB who steps out aggressively (but not necessarily recklessly) to engage early, attacks the duel, and tries to stop actions before they develop.</t>
+          <t>A high card discipline value should be interpreted as clean duel management with low booking and dismissal exposure.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be a flat-footed defender?</t>
+          <t>What are the most important attributes for a CB (or CB-pair) at a high-level?</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>When describing a CB to be flat-footed defender, it refers to a CB who is slow to react and often fails to engage early in (ground) duels, stays in place allowing opponents to approach without challenge.</t>
+          <t>The most important attribute for a CB (or CB-pair) is undeniably defensive capability, as their main job is to prevent the opposing team from scoring. Some good CBs (or CB-pairs) are good at only (ground or aerial) duel success rate, but in the modern game, it is almost necessary for a CB (-pair) to be good in other aspects in order to succeed.
+Some teams rely on CBs (-pairs) to contribute by winning possession after (ground or aerial) duels, perform clean defending while maintaining good card discipline, and intercept passes; other teams, on the other hand, desire someone who can read the game and tactically organize the defense, has the vision and anticipation to constantly keep the opposing's strikers off-side, communicate effectively with leadership; some other teams desire their CB(s) to possess the skill to build up play through quality ball-passing, by switching play effectively through long balls, and successfully breaking the opponent's first few pressure lines using short or long passes.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be dominant?</t>
+          <t>What are (at a low-level) the most important metrics within the ground duels quality for a CB (or CB-pair)?</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>When describing a CB, dominant means they excel in winning ground duels consistently, imposing themselves physically (+ mentally, in terms of concentration), and maintaining defensive stability.</t>
+          <t>The ranking order of importance of the ground duels' metrics (from most to least important) are:
+1) Possession win rate, 
+2) (Ground) Duel success rate, 
+3) (Ground) Interceptions per-90, 
+4) Discipline, 
+5) Card discipline, 
+6) Ground duels per-90. 
+The reasoning behind the specific ranking of these metrics is that it reflects a balanced evaluation of defensive effectiveness on the ground, with the greatest emphasis placed on actions that both stop the opponent and generate a positive outcome for the team.
+- Possession win rate is ranked first because it captures the most valuable result of a ground duel: not just disrupting the opposition, but regaining control of the ball in a way that can immediately support defensive stability or transition play.
+- (Ground) Duel success rate is placed second because it provides the strongest general indicator of a CB's effectiveness and reliability in one-versus-one ground contests across different situations.
+- (Ground) Interceptions per-90 is ranked third because it measures a player's ability to read the game, anticipate passing lanes, and break up opposition moves before they fully develop, which adds an important layer of defensive value beyond direct dueling.
+- Discipline is placed next because success in ground defending must also be judged by a player's ability to challenge aggressively without conceding unnecessary fouls, especially in dangerous areas or under pressure.
+- Card discipline is also relevant, but it is ranked slightly lower because cards are relatively infrequent events and therefore tend to be a less stable measure than broader disciplinary behavior, and
+- Ground duels per-90 is ranked last because it is mainly an involvement metric: it shows how often a player is engaged in ground contests, but high volume alone does not necessarily reflect defensive quality and is often shaped by team structure, match dynamics, and the amount of defending a player is required to do.
+Overall, this ranking prioritizes effective, team-beneficial defensive actions first, while still accounting for anticipation, control, discipline, and involvement. If the goal were instead to identify the most aggressive or most frequently tested ground defenders, then volume-based measures could be weighted more heavily; however, overemphasizing those metrics risks rewarding exposure and tactical circumstance rather than true defensive efficiency and value.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be an aggressive defender?</t>
+          <t>Could you answer some questions about aerial duels for me?</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>When describing a CB to be an aggressive defender (but not necessarily reckless), it refers to a CB who is proactive in initiating challenges to engage early in physical confrontations to win (ground) duels, does not wait passively, attacks spaces, and presses opponents.</t>
+          <t>Indeed — keep them heading my way! I'll do my best to win the second balls too.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be an overaggressive defender?</t>
+          <t>Which metrics are used to evaluate aerial duels for CBs?</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>When describing a CB to be an overaggressive defender, it refers to a CB who is too eager to step out (resulting in leaving unprotected space behind them) or tackle, sometimes resulting in excessively aggressive challenges, often taking unnecessary risks and making poor decisions that can lead to mistakes or bookings.</t>
+          <t>Currently, I have the capability to assess the following aerial duels' metrics for CB: 
+- Possession win rate, 
+- Duel success rate, 
+- Aerial wins per-90, 
+- Discipline, 
+- Card discipline, and 
+- Aerial duels per-90.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be soft?</t>
+          <t>May I ask you another question related to aerial duels?</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>When describing a CB to be soft, it refers to a CB who is easily outmaneuvered in (ground) duels, often lacking aggression and physical resistance, or determination to win confrontations as they do not challenge the duel with enough intensity and conviction.</t>
+          <t>No need to even ask, head them my way — I contest you to an (aerial) duel of Q&amp;As.
+Feel free to ask as many questions as you want — let's bring the ball down!</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be a passive defender?</t>
+          <t>What does aerial duels per-90 measure?</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>When describing a CB to be a passive defender, it refers to a CB who tends to not engage early enough in challenges, often staying back and allowing opponents too much time to approach before engaging in (ground) duels.</t>
+          <t>Aerial duels per-90 measures how many aerial duels a CB is involved in on average every 90 minutes of play. This helps to understand how active a player is in aerial duels relative to their playing time.
+A higher aerial duels per-90 indicates that the CB is more frequently engaging in defensive aerial contests, which can be a sign of their involvement and influence in defensive actions during matches. However, it's important to consider this metric in conjunction with success rates and other quality metrics, as a high volume of duels doesn't necessarily mean effective defending if the success rate is low.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be rash?</t>
+          <t>What is the aerial wins per-90 metric?</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>When describing a CB, rash means they are jumping into (ground) duels too quickly, overly aggressive and takes unnecessary risks in (ground) duels, often leading to poor decision-making and potential mistakes. Sometimes they mistime their challenges, resulting in receiving bookings.</t>
+          <t>Aerial wins per-90 quantifies how many aerial duels a CB wins on average every 90 minutes of play. This helps understanding how effective a player is at anticipating and making contact with the ball first (i.e. before the other aerial challengers involved do so) during aerial contests relative to their playing time.
+A higher aerial wins per-90 indicates that the CB is more frequently successful in aerial challenges (either defensively or offensively, both in play or during set-pieces) during a single match, which can be a sign of their effectiveness. However, it's important to consider this metric in combination with other of the aerial duels' quality metrics.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be error-prone?</t>
+          <t>What are (at a low-level) the most important metrics within the aerial duels quality for a CB (or CB-pair)?</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>When describing a CB, error-prone means they make frequent mistakes in (ground) duels, such as poor timing, incorrect positioning, or suboptimal decision-making under pressure, leading to dangerous situations for their team.</t>
+          <t>The ranking order of importance (from most to least) of the aerial duels' metrics are:
+1) Possession win rate, 
+2) (Aerial) Duel success rate, 
+3) Aerial wins per-90, 
+4) Discipline, 
+5) Card discipline, 
+6) Aerial duels per-90. 
+The reasoning behind the specific ranking of these metrics is that it reflects a balanced assessment of aerial performance, with the greatest emphasis placed on winning contests in a way that creates clear value for the team.
+- Possession win rate is ranked first because it goes beyond simply making contact or recording an aerial win: it captures how often a player's aerial actions actually help the team secure the ball, making it the most directly useful indicator of practical impact.
+- (Aerial) Duel success rate is placed second because it provides the strongest general measure of a CB's effectiveness and reliability in contested aerial situations across a wide range of contexts.
+- Aerial wins per-90 follows as an important volume-based measure of how often a player successfully imposes himself in the air, but it is ranked below the two efficiency-oriented metrics because it can be influenced by team style, opponent tendencies, and the number of aerial situations a player is exposed to.
+- Discipline is included next because aerial ability must be evaluated alongside the player's capacity to compete physically without conceding unnecessary fouls, especially in dangerous areas.
+- Card discipline is also relevant, but it is ranked slightly lower because cards are less frequent events and therefore tend to be a less stable indicator than broader disciplinary behavior, and
+- Aerial duels per-90 is ranked last because it is primarily an involvement metric: it shows how often a player is engaged in aerial contests, but high volume alone does not necessarily indicate quality and is often heavily shaped by tactical and match context.
+Overall, this ranking prioritizes effective, team-beneficial aerial dominance first, while still accounting for physical control, discipline, and overall involvement. If the goal were instead to identify the most aggressive or most heavily tested aerial defenders, then the volume-based metrics could be weighted more heavily; however, overemphasizing those measures risks rewarding exposure and tactical circumstance rather than true aerial quality and efficiency.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be shaky?</t>
+          <t>Could you answer a few questions about ball-passing?</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>When describing a CB, shaky means they lack consistency in (ground) duels, often looking insecure or unreliable.</t>
+          <t>Naturally! I'm open wide - pass those questions over to me, and I'll ensure to do my best to help you progress up the pitch.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be an elite dueller?</t>
+          <t>Which metrics are used to evaluate ball passing for CBs?</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>When describing a CB to be an elite dueller, it refers to a CB who's very good in 1v1s, shoulder-to-shoulder actions, and physical contests.</t>
+          <t>Currently, I have the capability to assess the following ball passing metrics for CB: 
+- Number of passes per-90, 
+- Long pass accuracy, 
+- Progressive pass accuracy, 
+- Passes into the final third per-90, 
+- Progressive passes per-90, and 
+- Pass accuracy rate.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be sloppy?</t>
+          <t>May I ask you another question?</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>When describing a CB, sloppy means they are untidy in possession or unskilled in basic defending notions.</t>
+          <t>Go ahead — feel free to switch the play over to me, and ask as many questions as you may need! Let's keep those questions in circulation.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be a no-nonsense defender?</t>
+          <t>What does number of passes per-90 measure?</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>When describing a CB to be a no-nonsense defender, it refers to a CB who is simple, reliable, direct, efficient, and focused on the task at hand by prioritizing clearing danger without unnecessary flair or risk-taking.</t>
+          <t>Number of passes per-90 measures how many passes a CB makes on average every 90 minutes of play. This helps to understand the player's involvement in ball circulation, their ability to maintain possession, and their intention to build up play.
+A higher number of passes per-90 indicates that the CB is more frequently involved in passing actions, which can be a sign of their influence in the team's attacking play. However, it's important to consider this metric in conjunction with pass accuracy and other ball-passing quality metrics, as a high volume of passes doesn't necessarily mean effective passing if the success rate is low.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to get rolled?</t>
+          <t>What does it imply if a CB (or CB-pair) is good or excellent in terms of number of passes per-90?</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>When describing a CB, getting rolled means that opponents (generally strikers) can pin them and turn them over.</t>
+          <t>A CB (or CB-pair) who is good or excellent in terms of number of passes per-90 is frequently involved in ball circulation, indicating their active participation and influence in the team's attacking play. This suggests the CB is highly effective in maintaining possession and contributing to the team's build-up play.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to overcommit?</t>
+          <t>What does it imply if a CB (or CB-pair) is below average or poor in terms of number of passes per-90?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>When describing a CB to be overcommitting, it refers to a CB who steps out and leaves their defending zone too readily, resulting in leaving unprotected space behind them.</t>
+          <t>A CB (or CB-pair) who is below average or poor in terms of number of passes per-90 is not frequently involved in ball circulation, indicating a lack of active participation in the team's attacking play. This suggests the CB may struggle with maintaining possession and contributing to the team's build-up play.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>What does it mean for a CB (or CB-pair) to be a liability?</t>
+          <t>What does long pass accuracy measure?</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>When describing a CB to be a liability, it refers to a CB who is a burden to their team, performing poorly across almost all defensive metrics, often making costly mistakes or being ineffective in crucial moments.</t>
+          <t>Long pass accuracy measures the proportion of successful long passes completed relative to the total number of long passes attempted by a CB. This metric is crucial for understanding a CB's ability to distribute the ball effectively over longer distances, which can be vital for initiating attacks and maintaining possession in the final third of the pitch. 
+A higher long pass accuracy indicates that a CB is more reliable in their long passing, inherently has an acute tactical vision, contributing to their team's ability to create scoring opportunities and maintain control of the game.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be a solid partnership?</t>
+          <t>What does it imply if a CB (or CB-pair) is outstanding in terms of long pass accuracy?</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, solid partnership refers to a CB pair or duo who are a reliable pair with few obvious weaknesses.</t>
+          <t>A CB (or CB-pair) who is outstanding in terms of long pass accuracy is highly effective in distributing the ball over longer distances, which can be vital for initiating attacks or switching play, and maintaining possession in the final third of the pitch. This indicates the CB has an acute tactical vision and is reliable in their long passing, contributing to their team's ability to create scoring opportunities and maintain control of the game.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be a well-balanced pair?</t>
+          <t>What are progressive passes?</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, well-balanced pair refers to a CB pair or duo where each CB complements each other's strengths and weaknesses, creating a more robust defensive unit.</t>
+          <t>Progressive passes are defined as passes that advance the ball towards the opponent's box (or goal) by: 
+- at least 30 meters closer to the opponent's goal if the starting and finishing points are within a team's own half, 
+- at least 15 meters closer to the opponent's goal if the starting and finishing points are in different halves of the pitch, or 
+- at least 10 meters closer to the opponent's goal if the starting and finishing points are in the opponent's half.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be a complementary partnership?</t>
+          <t>What does progressive pass accuracy measure?</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, complementary partnership refers to a CB pair or duo where their strengths cover each other's weaknesses, creating a more effective defensive unit.</t>
+          <t>Progressive passes are defined as passes that advance the ball towards the opponent's box (or goal) by: 
+- at least 30 meters closer to the opponent's goal if the starting and finishing points are within a team's own half, 
+- at least 15 meters closer to the opponent's goal if the starting and finishing points are in different halves of the pitch, or 
+- at least 10 meters closer to the opponent's goal if the starting and finishing points are in the opponent's half. 
+Hence, progressive pass accuracy measures the proportion of successful progressive passes completed relative to the total number of progressive passes attempted by a CB. This metric is crucial for understanding a CB's ability to advance the ball up the pitch and create potentially dangerous plays that might lead to goal-scoring opportunities. 
+A higher progressive pass accuracy indicates that a CB is more effective in advancing the ball towards the opponent's goal, contributing to their team's build-up attacking play and increasing the likelihood of creating goal-scoring opportunities.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be an established pairing?</t>
+          <t>What does passes to final third per-90 measure?</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, an established pairing refers to a settled CB pair or duo with continuity (i.e. has played many minutes and matches together on the pitch), that has developed a strong understanding and defensive coordination over time.</t>
+          <t>Passes to final third per-90 quantifies the number of successful passes that are threaded into the final third of the pitch per 90 minutes played by a CB (or CB-pair). This metric is vital for understanding their skill to contribute to their team's attacking play, creating potentially dangerous or goal-scoring opportunities. This metric also measures a CB's (or CB-pair's) willingness to attempt to find high-value passing options. 
+A higher passes to final third per-90 value demonstrates tactical vision and an eye for finding high-value passing options; thus, it shows that a CB is more effective in advancing the ball towards and close to the opponent's box (or goal) and contributing to their team's build-up attacking play.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be cohesive?</t>
+          <t>What does it imply if a CB (or CB-pair) is average in terms of passes to final third per-90?</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, cohesive means a CB pair or duo that demonstrates great coordination, moving and defending as a unit.</t>
+          <t>A CB (or CB-pair) who is average in terms of passes to final third per-90 is contributing at a moderate level to their team's attacking play, neither excelling nor struggling significantly. This suggests the CB is helping to advance the ball into the final third but may have room for improvement in terms of finding higher-value passing options and creating more goal-scoring opportunities or helping their team maintain possession as they intend to progress into the final third of the pitch.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be in sync?</t>
+          <t>What does progressive passes per-90 quantify?</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, being in sync means they are well-coordinated and move together effectively during defensive actions: good timing in stepping, dropping, and covering.</t>
+          <t>Progressive passes are defined as passes that advance the ball towards the opponent's box (or goal) by: 
+- at least 30 meters closer to the opponent's goal if the starting and finishing points are within a team's own half, 
+- at least 15 meters closer to the opponent's goal if the starting and finishing points are in different halves of the pitch, or 
+- at least 10 meters closer to the opponent's goal if the starting and finishing points are in the opponent's half. 
+Thus, progressive passes per-90 quantifies the number of passes that advance the ball towards the opponent's box (or goal) per 90 minutes played. This metric is very important for assessing a CB's predisposition to attempt passes of this nature. 
+A higher progressive passes per-90 value indicates a CB's skill for offensive tactical vision, their ability to effectively advance the ball towards the opponent's goal, and contribute to their team's attacking play.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be well-drilled?</t>
+          <t>What does it imply if a CB (or CB-pair) is good in terms of progressive passes per-90?</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, being well-drilled means they look tactically coached and coordinated, have practiced and refined their defensive movements and communications to a high level of proficiency.</t>
+          <t>A CB (or CB-pair) who is good in terms of progressive passes per-90 is effectively advancing the ball towards the opponent's goal, demonstrating strong offensive tactical vision and the ability to create goal-scoring opportunities. This indicates they are contributing positively to their team's attacking play.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be a stable pairing?</t>
+          <t>What are (at a low-level) the most important metrics within the ball-passing quality for a CB (or CB-pair)?</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, a stable pairing refers to a duo that has demonstrated consistency and reliability over time, with minimal fluctuations in performance — thus, showing low-variance, trustworthy behavior.</t>
+          <t>The ranking order of importance (from most to least) of the ball-passing metrics are:
+1) Pass accuracy rate, 
+2) Progressive passes per-90, 
+3) Passes to final third per-90, 
+4) Progressive pass accuracy, 
+5) Long pass accuracy, 
+6) Number of passes per-90. 
+The reasoning behind the specific ranking of these metrics is that it reflects a deliberately balanced profile rather than an evaluation model focused purely on progression efficiency.
+- Pass accuracy rate is ranked first because it is the strongest baseline signal of passing reliability: it is based on a large sample of actions, tends to be more stable than the other metrics, and is directly tied to possession security and clean build-up play,
+- Progressive passes per-90 is placed second because it captures a CB's ability to play proactive, line-breaking passes that move the team forward,
+- Passes to the final third per-90 follows as another strong indicator of territorial progression, although it is somewhat more dependent on team structure and tactical context than general progression metrics,
+- Progressive pass accuracy is also important, but it is ranked slightly lower because it is typically calculated from a smaller number of attempts, making it less stable than overall pass accuracy,
+- Long pass accuracy remains useful, particularly for assessing direct distribution, but it is often highly role- and system-dependent and can fluctuate more because long passes usually occur at lower volumes, and
+- Number of passes per-90 is ranked last because it mainly reflects involvement and availability in possession rather than passing quality or value creation in itself.
+Overall, this ranking favors a well-rounded passing profile that balances reliability, progression, and involvement. If the goal were instead to identify which CBs (or CB-pairs) truly add value through difficult passing, then progressive and long-pass efficiency could be weighted more heavily; however, overemphasizing those metrics can unintentionally reward low-risk or low-volume samples, as well as players operating in specific tactical niches, with long-pass accuracy in particular becoming unstable without attempt-volume controls.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be a top-class axis?</t>
+          <t>What does it mean for a CB (or CB-pair) to be a front-foot defender?</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, a top-class axis refers to a duo that demonstrates exceptional performance and synergy, setting a high standard for defensive excellence.</t>
+          <t>When describing a CB to be front-foot defender, it refers to a CB who steps out aggressively (but not necessarily recklessly) to engage early, attacks the duel, and tries to stop actions before they develop.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>What does it mean for a CB-pair to be a shaky pair?</t>
+          <t>What does it mean for a CB (or CB-pair) to be a flat-footed defender?</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>When describing a CB-pair, a shaky pair means a duo that lacks consistency and reliability, often showing significant fluctuations in performance — thus, displaying high-variance, unpredictable behavior. They often commit many fouls and receive many bookings as well, which can be a concern for their own team.</t>
+          <t>When describing a CB to be flat-footed defender, it refers to a CB who is slow to react and often fails to engage early in (ground) duels, stays in place allowing opponents to approach without challenge.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>How is the ground duelling quality score assessed for CBs (or CB-pairs)?</t>
+          <t>What does it mean for a CB (or CB-pair) to be dominant?</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The ground duelling quality score is assessed by aggregating the (standardized) individual ground duels' metrics (`z_metric`), together with their respective importance weights (`w_metric`) resulting in (`Zq_raw`). Then `Zq_raw` is further standardized again to `Z_q` to put it on a common scale to make it easy for interpretation and to compare CBs (or CB-pairs) across seasons or leagues.</t>
+          <t>When describing a CB, dominant means they excel in winning ground or aerial duels consistently, imposing themselves physically (+ mentally, in terms of concentration), and maintaining defensive stability.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>How are (CB) pair-level raw metrics computed?</t>
+          <t>What does it mean for a CB (or CB-pair) to be an aggressive defender?</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Each CB-pair raw metric is the equal-weight average of the two CBs' (or CB-pairs') raw values. 
-For example, `Ground Duels Per-90 (Pair-Level) = (CB_1's Ground Duels Per-90 + CB_2's Ground Duels Per-90) / 2`.</t>
+          <t>When describing a CB to be an aggressive defender (but not necessarily reckless), it refers to a CB who is proactive in initiating challenges to engage early in physical confrontations to win (ground or aerial) duels, does not wait passively, attacks spaces, and presses opponents.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>How are (CB) pair-level z-score metrics represented?</t>
+          <t>What does it mean for a CB (or CB-pair) to be an overaggressive defender?</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Each CB-pair z-score metric is the equal-weight average of the two CBs' (or CB-pairs') z-score values. 
-For example, `Ground Duels Per-90 z-score (Pair-Level) = (CB_1's Ground Duels Per-90 z-score + CB_2's Ground Duels Per-90 z-score) / 2`.</t>
+          <t>When describing a CB to be an overaggressive defender, it refers to a CB who is too eager to step out (resulting in leaving unprotected space behind them) or tackle, sometimes resulting in excessively aggressive challenges, often taking unnecessary risks and making poor decisions that can lead to mistakes or bookings.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>How is the overall (ground duels) quality of the CB-pair defined?</t>
+          <t>What does it mean for a CB (or CB-pair) to be soft?</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The overall (ground duels) quality of the CB-pair is the same as the weighted CB-pair mean; defined as the average of all the individual (ground duels) metrics together of both CBs, weighted by their importance. 
-`(Ground Duels) Quality of CB-Pair = Σ (Importance Weight for Metric `m` * CB-Pair Mean for Metric `m`). 
-**Reminder:** The weights for each metric must sum to `1.0`, and can be adjusted by yourself using the UI sliders in this page, to reflect the relative importance of each metric in the overall (ground duels) quality of the CB-pair. 
-A higher overall (ground duels) quality indicates that the CB-pair is stronger across the weighted metrics, on average.</t>
+          <t>When describing a CB to be soft, it refers to a CB who is easily outmaneuvered in (ground or aerial) duels, often lacking aggression and physical resistance, or determination to win confrontations as they do not challenge the duel with enough intensity and conviction.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>What is the coverage/complementarity bonus in CB-pairings?</t>
+          <t>What does it mean for a CB (or CB-pair) to be a passive defender?</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The coverage or complementarity bonus is how well the 2 CBs' strengths complement each other, for example, one is strong in metric A, the other in metric B, so they cover more quality dimensions as a pair). 
-`Complementariy of CB-Pair = Σ [Importance Weight for Metric `m` * (CB-Pair Best for Metric `m` - CB-Pair Mean for Metric `m`)]. 
-**Reminder:** The weights for each metric must sum to `1.0`, and can be adjusted by yourself using the UI sliders in this page, to reflect the relative importance of each metric in the overall (ground duels) quality of the CB-pair. 
-A higher coverage/complementarity bonus indicates that the CB-pair has more complementary strengths across the weighted metrics.</t>
+          <t>When describing a CB to be a passive defender, it refers to a CB who tends to not engage early enough in challenges, often staying back and allowing opponents too much time to approach before engaging in (ground or aerial) duels.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>What is understood by the floor of a CB-pair?</t>
+          <t>What does it mean for a CB (or CB-pair) to be rash?</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A.k.a. the weak-link protection of the pair, the floor of the CB-pair is based on the weaker CB's score for each metric, weighted by importance. This captures the idea that a pair is only as strong as its weaker link in each dimension (metric, in our case). 
-`Floor of CB-Pair = Σ (Importance Weight for Metric `m` * CB-Pair Worst for Metric `m`). 
-**Reminder:** The weights for each metric must sum to `1.0`, and can be adjusted by yourself using the UI sliders in this page, to reflect the relative importance of each metric in the overall (ground duels) quality of the CB-pair. 
-A higher floor indicates that the weaker CB in the pair is still performing at a relatively strong level across the weighted metrics, which can be a positive attribute for the overall stability and reliability of the CB-pair.</t>
+          <t>When describing a CB, rash means they are jumping into (ground or aerial) duels too quickly, overly aggressive and takes unnecessary risks in (ground or aerial) duels, often leading to poor decision-making and potential mistakes. Sometimes they mistime their challenges, resulting in receiving bookings.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>How are the overall (ground duels) quality, coverage/complementarity bonus, and floor factors/components of a CB-pair put on a common scale?</t>
+          <t>What does it mean for a CB (or CB-pair) to be error-prone?</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Each factor, or component, is standardized into its respective z-score.</t>
+          <t>When describing a CB, error-prone means they make frequent mistakes in (ground or aerial) duels or ball-passing, such as poor timing, incorrect positioning, mistakenly passing the ball to the opponent or making passes that are easy to intercept, or demonstrating suboptimal decision-making under pressure, leading to dangerous situations for their team.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>How do you calculate the CB-pair fit score, to give an overall evaluation of how the CB duo would potentially perform and fit together, if they were to be paired and play together?</t>
+          <t>What does it mean for a CB (or CB-pair) to be shaky?</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The CB-pair fit score is a weighted sum of the standardized components: overall (ground duels) quality, coverage/complementarity bonus, and floor factors/components of a CB-pair. 
-`CB-Pair Fit Score = Σ (CB-Pair Fit Weight for Component `c` * CB-Pair Fit Component z-score `c_z`). 
-**Note:** The weights for each component can be adjusted by yourself, using the UI sliders in this page, to reflect the relative importance of each factor in the overall CB-pair fit score. 
-A higher CB-pair fit score indicates a stronger potential fit and performance of the CB duo when paired together, considering their overall quality, how well they complement each other, and the strength of their weaker link.</t>
+          <t>When describing a CB, shaky means they lack consistency in (ground or aerial) duels or ball-passing, often looking insecure or unreliable.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>How should a CB-pair with high overall (ground duels) quality but low coverage/complementarity bonus be interpreted?</t>
+          <t>What does it mean for a CB (or CB-pair) to be an elite dueller?</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>It indicates strong average level but weaker mutual coverage across metrics.</t>
+          <t>When describing a CB to be an elite dueller, it refers to a CB who's very good in 1v1s, shoulder-to-shoulder actions, and physical contests.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>How should low (CB-pair) floor be interpreted?</t>
+          <t>What does it mean for a CB (or CB-pair) to be sloppy?</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Low (CB-pair) floor indicates weak-link risk where one CB can pull down the duo in difficult (ground) duel contexts.</t>
+          <t>When describing a CB, sloppy means they are untidy in possession or unskilled in basic defending notions.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>What's understood by (directional) CB(-pair) companion/partner fit?</t>
+          <t>What does it mean for a CB (or CB-pair) to be a no-nonsense defender?</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Global CB-pair fit is symmetric, but companion/partner choice is directional. The companion/partner fit score captures how well one CB (the companion or partner) can cover the deficits of another CB (the anchor) in a directional way, meaning that the fit is evaluated from the perspective of the anchor CB and how well the companion/partner CB can complement and cover their weaknesses. 
-This allows for a more nuanced evaluation of potential pairings, as it considers not only the overall fit of the duo but also how well one CB can specifically address the weaknesses of the other, which is crucial for building effective defensive partnerships. 
-`Companion/Partner Fit Score = Σ (Companion/Partner Fit Weight for Component `c` * Companion/Partner Fit Component z-score `c_z`). 
-A higher companion/partner fit score indicates that the companion/partner CB has strengths that effectively cover the anchor CB's weaknesses across the weighted metrics, suggesting a potentially strong fit as a CB-pair from the anchor's perspective.</t>
+          <t>When describing a CB to be a no-nonsense defender, it refers to a CB who is simple, reliable, direct, efficient, and focused on the task at hand by prioritizing clearing danger without unnecessary flair or risk-taking.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Why is companion fit directional while pair fit is symmetric?</t>
+          <t>What does it mean for a CB (or CB-pair) to get rolled?</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pair fit is one shared global profile, but deficit-coverage gain depends on which CB is treated as the anchor.</t>
+          <t>When describing a CB, getting rolled means that opponents (generally strikers) can pin them and turn them over.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>How are anchor CB deficits computed in the CB(-pair) companion/partner fit model?</t>
+          <t>What does it mean for a CB (or CB-pair) to overcommit?</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>For each weighted z-score metric, the anchor CB's deficit is calculated as: `max(0.0, -Anchor CB's z-score Metric `z_m`)`. 
-This means that if the anchor CB's z-score for a particular metric is negative (indicating below-average performance), the deficit will be the positive value of that z-score (representing how much they are below average). If the anchor CB's z-score is `0.0` or positive (indicating average or above-average performance), the deficit will be `0.0`, as there is no weakness to cover in that metric. 
-A higher anchor CB deficit in a particular metric indicates a greater weakness in that area, which the companion/partner CB can potentially cover with their strengths.</t>
+          <t>When describing a CB to be over-committing, it refers to a CB who steps out and leaves their defending zone too readily, resulting in leaving unprotected space behind them.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>How is companion/partner CB coverage computed for each anchor deficit?</t>
+          <t>What does it mean for a CB (or CB-pair) to be a liability?</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Coverage per z-score metric is calculated as: `min[Anchor CB's Deficit, max(0.0, Companion/Partner CB's z-score Metric `z_m`)]`. 
-This means that the coverage for each metric is the lesser of the anchor CB's deficit and the companion/partner CB's positive z-score for that metric. If the companion/partner CB's z-score is negative or `0.0`, it does not provide any coverage for that metric, resulting in a coverage of `0.0`. If the companion/partner CB's z-score is positive, it can provide coverage up to the amount of the anchor CB's deficit, but not exceeding it. 
-A higher coverage value for a particular metric indicates that the companion/partner CB has a stronger ability to cover the anchor CB's weakness in that area.</t>
+          <t>When describing a CB to be a liability, it refers to a CB who is a burden to their team, performing poorly across almost all defensive metrics, often making costly mistakes or being ineffective in crucial moments.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>How is the raw deficit-coverage gain computed?</t>
+          <t>What does it mean for a CB-pair to be a solid partnership?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The raw deficit-coverage gain is the weighted sum of metric-level coverage values across all weighted z-score metrics. For each anchor CB `CB_1`, we compute deficits on each weighted metric's z-score and quantify how much partner `CB_2` covers those deficits. Then, this deficit-coverage gain signal is blended with the global CB-pair fit score. 
-This captures how well the partner's (`CB_2`) strengths can compensate for the anchor's (`CB_1`) weaknesses in each metric dimension, which is a key aspect of their potential fit as a pair. 
-`Companion Fit Score for Partner `CB_2` as Companion to Anchor `CB_1` = Σ (Importance Weight for Metric `m` * Deficit-Coverage Gain for Metric `m`). 
-**Note:** The weights for each component can be adjusted by yourself, using the UI sliders in this page, to reflect the relative importance of each factor in the overall companion fit score. 
-A higher companion fit score indicates that the partner `CB_2` has strengths that effectively cover the anchor `CB_1`'s weaknesses across the weighted metrics, suggesting a potentially strong fit as a CB-pair.</t>
+          <t>When describing a CB-pair, solid partnership refers to a CB pair or duo who are a reliable pair with few obvious weaknesses.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>What is deficit-coverage gain (z-score) within the anchor CB?</t>
+          <t>What does it mean for a CB-pair to be a well-balanced pair?</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>It is the within-anchor standardization (z-score) of the raw deficit-coverage gain so that partner CB options are compared on the same anchor CB baseline.</t>
+          <t>When describing a CB-pair, well-balanced pair refers to a CB pair or duo where each CB complements each other's strengths and weaknesses, creating a more robust defensive unit.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>How is a CB companion/partner fit rank interpreted?</t>
+          <t>What does it mean for a CB-pair to be a complementary partnership?</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>It is the rank of each potential partner/companion CB inside only one anchor CB's pool set of candidate partners/companions.</t>
+          <t>When describing a CB-pair, complementary partnership refers to a CB pair or duo where their strengths cover each other's weaknesses, creating a more effective defensive unit.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>How should high deficit-coverage gain (within the specified anchor CB) with modest global CB-pair fit score be interpreted?</t>
+          <t>What does it mean for a CB-pair to be an established pairing?</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>It signals that the partner CB has strong complementary strengths that can cover the anchor CB's weaknesses, even if their overall fit as a pair is only moderate.</t>
+          <t>When describing a CB-pair, an established pairing refers to a settled CB pair or duo with continuity (i.e. has played many minutes and matches together on the pitch), that has developed a strong understanding and defensive coordination over time.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>How should high global CB-pair fit score with weak deficit-coverage gain be interpreted?</t>
+          <t>What does it mean for a CB-pair to be cohesive?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>It indicates that while the partner CB may not specifically cover the anchor CB's weaknesses, they still have a strong overall fit as a pair based on their general performance and compatibility across metrics.</t>
+          <t>When describing a CB-pair, cohesive means a CB pair or duo that demonstrates great coordination, moving and defending as a unit.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>What does it mean for a CB-pair to be in sync?</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>When describing a CB-pair, being in sync means they are well-coordinated and move together effectively during defensive actions: good timing in stepping, dropping, and covering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>What does it mean for a CB-pair to be well-drilled?</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>When describing a CB-pair, being well-drilled means they look tactically coached and coordinated, have practiced and refined their defensive movements and communications to a high level of proficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>What does it mean for a CB-pair to be a stable pairing?</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>When describing a CB-pair, a stable pairing refers to a duo that has demonstrated consistency and reliability over time, with minimal fluctuations in performance — thus, showing low-variance, trustworthy behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>What does it mean for a CB-pair to be a top-class axis?</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>When describing a CB-pair, a top-class axis refers to a duo that demonstrates exceptional performance and synergy, setting a high standard for defensive excellence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>What does it mean for a CB-pair to be a shaky pair?</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>When describing a CB-pair, a shaky pair means a duo that lacks consistency and reliability, often showing significant fluctuations in performance — thus, displaying high-variance, unpredictable behavior. They often commit many fouls and receive many bookings as well, which can be a concern for their own team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>How is the ground duelling (or ground duels) quality score assessed for CBs (or CB-pairs)?</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>The ground duelling quality score is assessed by combining the key ground-duel metrics into one overall index, after first standardizing them so they can be compared on the same scale - this makes it easy for interpretation and also to compare CBs (or CB-pairs) across seasons or leagues. At a high level, it rewards the most valuable defensive outcomes the most — especially winning possession back, succeeding in duels, reading danger through interceptions, and defending cleanly without unnecessary fouls or bookings — while still accounting for duel involvement. These standardized metrics are then combined using importance weights to produce a raw composite score, which is standardized again into a final z-score so that CBs (or CB-pairs) can be compared clearly against the rest of their sample.
+For CB-pairs specifically, the overall ground-duels quality reflects the weighted average of the pair's shared metric profile, while the broader CB-pair fit score goes one step further by also considering complementarity and weak-link protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>How is the aerial duelling (or aerial duels) quality score assessed for CBs (or CB-pairs)?</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>The aerial duelling quality score is evaluated by combining the key aerial-duel metrics into one overall index, after first standardizing them so they can be compared on the same scale - this makes it easy for interpretation and also to compare CBs (or CB-pairs) across seasons or leagues. At a high level, it rewards the most valuable aerial outcomes the most — especially regaining possession, succeeding in aerial contests, and consistently winning aerial actions — while also accounting for clean defending and duel involvement. These standardized metrics are then combined using importance weights to produce a raw composite score, which is standardized again into a final z-score so that CBs (or CB-pairs) can be compared clearly against the rest of their sample.
+For CB-pairs specifically, the overall aerial-duels quality reflects the weighted average of the pair's shared aerial profile, while the broader CB-pair fit score goes one step further by also considering complementarity and weak-link protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>How is the ball-passing quality score assessed for CBs (or CB-pairs)?</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>The ball-passing quality score is assessed by combining the main ball-passing metrics into one overall index, after first standardizing them so they can be compared fairly on the same scale - this makes it easy for interpretation and also to compare CBs (or CB-pairs) across seasons or leagues. At a high level, it rewards the most valuable passing behaviors the most — especially pass reliability, progressive passing output, and the ability to move the ball into areas high up the pitch — while also accounting for progressive and long-pass execution, with simple passing volume playing a smaller supporting role. These standardized metrics are then combined using importance weights to produce a raw composite score, which is standardized again into a final z-score so that CBs (or CB-pairs) can be compared clearly against the rest of their sample.
+For CB-pairs specifically, the overall ball-passing quality reflects the weighted average of the pair's shared passing profile, while the broader CB-pair fit score also considers complementarity and weak-link protection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>How are (CB) pair-level raw metrics computed?</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Each CB-pair raw metric is the equal-weight average of the two CBs' (or CB-pairs') raw values. 
+For example, `Ground/Aerial Duels or Ball-Passing Per-90 (Pair-Level) = (CB_1's Ground/Aerial Duels or Ball-Passing Per-90 + CB_2's Ground/Aerial Duels or Ball-Passing Per-90) / 2`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>How are (CB) pair-level z-score metrics represented?</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Each CB-pair z-score metric is the equal-weight average of the two CBs' (or CB-pairs') z-score values. 
+For example, `Ground/Aerial Duels or Ball-Passing Per-90 z-score (Pair-Level) = (CB_1's Ground/Aerial Duels or Ball-Passing Per-90 z-score + CB_2's Ground/Aerial Duels or Ball-Passing Per-90 z-score) / 2`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>How is the overall ground duels quality of the CB-pair defined?</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>For CB-pairs specifically, the overall ground-duels quality reflects the weighted average of the pair's shared ground profile (i.e. of all the individual ground duels-related metrics of both CBs together, weighted by their importance), while the broader CB-pair fit score goes one step further by also considering complementarity and weak-link protection.
+A higher overall ground duels quality indicates that the CB-pair is stronger across the weighted metrics, on average; thus, it suggests that the CB-pair is more effective in ground duels and can be a more reliable defensive unit in those contexts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>How is the overall aerial duels quality of the CB-pair defined?</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>For CB-pairs in particular, the overall aerial-duels quality represents the weighted average of the pair's shared aerial profile (i.e. of all the individual aerial duels-related metrics of both CBs together, weighted by their importance), while the broader CB-pair fit score goes one step further by also considering complementarity and weak-link protection.
+A higher overall aerial duels quality indicates that the CB-pair is stronger across the weighted metrics, on average; thus, it suggests that the CB-pair is more effective in aerial duels and can be a more reliable defensive unit in those contexts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>How is the overall ball-passing quality of the CB-pair defined?</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>For CB-pairs in particular, the overall ball-passing quality represents the weighted average of the pair's shared passing profile (i.e. of all the individual passing-related metrics of both CBs together, weighted by their importance), while the broader CB-pair fit score goes one step further by also considering complementarity and weak-link protection.
+A higher overall ball-passing quality indicates that the CB-pair is stronger across the weighted metrics, on average; thus, it suggests that the CB-pair is more effective in passing the ball and can be a more reliable unit in those contexts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>What is the coverage/complementarity bonus in CB-pairings?</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>The coverage or complementarity bonus captures how much the 2 CBs added different strengths to the same pair, rather than simply duplicating each other. At a high level, it rewarded duos where one CB was strong in quality dimensions that the other did not dominate, so the pair could cover more of the job across the weighted metrics. In ground or aerial duels, that could mean different ways of contesting, recovering, or intervening; in ball-passing, it could mean different but useful passing strengths.
+A higher complementarity bonus therefore suggested a more multidimensional pair, not just a pair with strong average quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>What is understood by the floor of a CB-pair?</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>The floor of a CB-pair referred to the weaker side of the partnership across the weighted metrics, so it reflected how safe the duo remained when its weaker link was exposed. Semantically, it was a weak-link protection concept: even if one CB was excellent, the pair could still become vulnerable if the other CB fell short in key areas.
+A high floor meant the duo did not collapse easily in its weaker dimensions, while a low floor meant opponents could more easily target the softer spots of the pair. In that sense, the floor was about stability and minimum standard, not peak quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>How are the overall (ground/aerial duels or ball-passing) quality, coverage/complementarity bonus, and floor factors/components of a CB-pair put on a common scale?</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>These 3 components are first measured in their own raw terms, but they do not naturally live on the same numerical scale. To combine them fairly, each one is standardized into a z-score relative to the rest of the sample, so they all become comparable as above- or below-average signals. This matters because overall quality, complementarity, and floor components describe different things and could vary differently across the population. Once standardized, they can be blended into one CB-pair fit score without one component dominating simply because of its original units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>How do you calculate the CB-pair fit score, to give an overall evaluation of how the CB duo would potentially perform and fit together, if they were to be paired and play together?</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>The CB-pair fit score is calculated by combining the standardized versions of 3 ingredients: the pair's overall quality level, its complementarity bonus, and its floor. At a high level, this means the model rewards duos that are good on average, balanced in how their strengths interact, and protect against weak-link risk. Each component is weighted and then summed on the common z-score scale to produce one overall fit value.
+A higher CB-pair fit score therefore suggests a pair that projects well not just because of talent, but because of how that talent is distributed across the duo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>How should a CB-pair with high overall (ground/aerial duels or ball-passing) quality but low coverage/complementarity bonus be interpreted?</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>This indicates a duo that is strong on average, but more because both players are individually good than because they cover different needs for each other. In semantic terms, the pair has level, but not much extra synergy from role balance or skill diversification. This could still produce a very good pairing, especially if both CBs are well-rounded, but it suggests less added upside from complementary strengths. In tougher match contexts, the duo might rely more on baseline quality than on one player offsetting the other's weaknesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>How should low (CB-pair) floor be interpreted?</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>A low floor indicates meaningful weak-link risk within the pair of CBs. Even if one CB offers strong quality, the weaker side of the duo could still drag the partnership down in key moments, whether in duels or in build-up phases. Semantically, it suggests instability under pressure: opponents might not need to beat the whole pair, only the softer dimension within it. This is why low-floor pairs could look acceptable on average but still feel fragile in practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>What's understood by (directional) CB(-pair) companion/partner fit?</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>(Directional) Companion or partner fit asks a different question from overall pair fit: not simply 'how good is this duo overall?', but 'how well does CB `B` help the CB `A` specifically?'. One CB is treated as the anchor, and the partner is assessed by how well he/she covers the anchor's weaker areas while still forming a strong overall pair. This makes the score more role-specific and decision-oriented for squad building.
+A high companion fit therefore means that the proposed partner is especially useful for that anchor, not just generally good.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Why is companion fit directional while pair fit is symmetric?</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Companion fit is directional because it depends on whose weaknesses are being covered. If CB `A` is the anchor, the model asks how much CB `B` helps `A`; if the anchor changes to CB `B`, the question changes as well, so the answer could change too.
+Pair fit, by contrast, is symmetric because it evaluates the shared duo as one combined profile, regardless of who is listed first. In other words, pair fit describes the partnership itself, while companion fit describes the partnership from one specific (CB) player's point of view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>How are anchor CB deficits computed in the CB(-pair) companion/partner fit model?</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Anchor deficits are computed from the anchor CB's below-average areas only within its metrics. At a high level, each weighted metric is checked to see whether the anchor sits below the sample baseline; if not, there is no deficit to cover in that dimension. This means the model does not reward a partner for 'covering' strengths the anchor already has. Semantically, the deficit profile is simply a map of where that anchor CB most needs help.
+A higher deficit in a particular metric means that the anchor CB is weaker in that area compared to the sample, so there is more room for a partner to add value by covering that weakness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>How is companion/partner CB coverage computed for each anchor deficit?</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>For each anchor deficit, the partner only receives coverage credit if he/she brings genuine positive strength in that same metric. The coverage is capped by the size of the anchor's weakness, so the model rewards useful coverage, not excess strength beyond what is needed. This keeps the interpretation practical: a partner helps most when he/she fills a real gap, not just when he/she is generally good. Semantically, it's a 'can this (CB) player patch this specific weakness?' calculation.
+A higher coverage for a particular deficit means that the partner CB is stronger in that area and can effectively help mitigate the anchor CB's weakness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>How is the raw deficit-coverage gain computed?</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>The raw deficit-coverage gain is the total amount of the anchor's weakness profile that the partner could cover across the weighted metrics. At a high level, it sums the partner's useful coverage in each relevant metric dimension, with more important metrics carrying more influence. It's therefore a targeted complementarity signal rather than a general quality score.
+A higher raw deficit-coverage gain means the partner addresses more of the anchor's actual needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>What is deficit-coverage gain (z-score) within the anchor CB?</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>The deficit-coverage gain z-score within the anchor is the standardized version of that raw coverage signal, but only against the anchor CB's own pool of possible partners. This matters because some anchors have larger or more coverable deficit profiles than others, so raw values are not always directly comparable across anchors. The within-anchor z-score tells you whether a given partner covers that anchor especially well relative to the alternatives available for that same anchor. In practice, it is the fairest way to compare companion options from one anchor's perspective.
+A higher deficit-coverage gain z-score within the anchor means that the partner is more effective at covering the anchor's weaknesses compared to other potential partners for that same anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>How is a CB companion/partner fit rank interpreted?</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>A CB companion or partner fit rank is interpreted inside one anchor CB's candidate-partner pool only. A rank of 1 (i.e. `#1`, equivalent to the best candidate partner) means that, for that specific anchor and that specific quality context, no other candidate in the sample projects as a better companion under the model. It is therefore a relative, anchor-specific ranking rather than a universal statement about the partner being the best CB overall. Semantically, it answers 'how good is this partner for him/her?' rather than 'how good is this player in absolute terms?'.
+A higher companion fit rank (i.e. closer to `#1`) means that the partner is more effective at covering the anchor's weaknesses compared to other potential partners for that same anchor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>How should high deficit-coverage gain (within the specified anchor CB) with modest global CB-pair fit score be interpreted?</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>This combination suggests a partner who is particularly useful for the anchor's weaknesses, even if the duo does not project as elite overall. In domain terms, the fit is locally strong but globally less dominant: the partner solves problems for that anchor, yet the total pair quality, balance, or floor may still only be moderate. This kind of profile could still be valuable in tailored squad-building decisions, especially if the aim is to support one specific starter. It points to a specialist-style fit rather than a universally top-tier pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>How should high global CB-pair fit score with weak deficit-coverage gain be interpreted?</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>This usually means the 2 CBs project well together overall, but not because the partner strongly repairs the anchor's specific weaknesses. The duo may still have strong average quality, a solid floor, or broadly compatible profiles, even if the anchor-specific coverage signal is limited. In practice, this points to a good general pairing rather than a highly customized one. So the partnership could still be strong, but its success would come more from overall level and balance than from targeted deficit repair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>I want to know about a CB?</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>Naturally — I'm always on hand for a CB assessment, like a CB sweeping up danger... who would you like to know about next? 
 Please select them from the drop-down list on the left!</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>I would like to assess another player</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Absolutely — let's keep the defensive line strong and bring in another CB... who would you like to know about next? 
 Please select them from the drop-down list on the left!</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>I want to analyze a CB duo?</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Definitely — let's put together another CB pairing worthy of a clean sheet... who would you like to know about next? 
 Please select them from the drop-down list on the left!</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>I would to analyze another CB-pair</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Happy to — there's always room for one more well-drilled CB duo in the back line... who would you like to know about next? 
 Please select them from the drop-down list on the left!</t>

--- a/data/describe/CBs_and_CB_Pairs.xlsx
+++ b/data/describe/CBs_and_CB_Pairs.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CBs or CB-Pairs holding metrics with z-score values: 
-- `≥ 1.5` = Outstanding, 
-- `1.5 &gt; z ≥ 1.0` = Excellent, 
-- `1.0 &gt; z ≥ 0.5` = Good, 
-- `0.5 &gt; z ≥ -0.5` = Average, 
-- `-0.5 &gt; z ≥ -1.0` = Below Average, 
+          <t>The interpretation mappings being used for different z-score ranges or values of (quality-related, fit-related, and component-related) metrics for the individual CBs, CB-Pairs, and Anchor CB-Companion CB analysis task type settings are:
+- `z ≥ 1.5` = Outstanding,
+- `1.5 &gt; z ≥ 1.0` = Excellent,
+- `1.0 &gt; z ≥ 0.5` = Good,
+- `0.5 &gt; z ≥ -0.5` = Average,
+- `-0.5 &gt; z ≥ -1.0` = Below Average, and
 - `-1.0 &gt; z` = Poor.</t>
         </is>
       </c>
@@ -2010,8 +2010,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Happy to — there's always room for one more well-drilled CB duo in the back line... who would you like to know about next? 
-Please select them from the drop-down list on the left!</t>
+          <t>Happy to — there's always room for one more well-drilled CB duo in the back line... who would you like to know about next?</t>
         </is>
       </c>
     </row>
